--- a/output/复旦链接开放协作平台-小程序功能蓝图.xlsx
+++ b/output/复旦链接开放协作平台-小程序功能蓝图.xlsx
@@ -18,6 +18,7 @@
     <sheet name="08 平台映射总表" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="09 驻沪领事馆名录" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="10 命名与表述规范" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11 中心公开新闻精选" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +45,7 @@
     <font>
       <name val="微软雅黑"/>
       <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="005C3D7A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -55,7 +56,7 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <color rgb="00222222"/>
+      <color rgb="001A0A2E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -66,11 +67,11 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <color rgb="00666666"/>
+      <color rgb="005C3D7A"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -79,12 +80,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00123F55"/>
+        <fgColor rgb="0057068C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F6F8"/>
+        <fgColor rgb="00F0E6F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,17 +95,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF2F4"/>
+        <fgColor rgb="00E8D8F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E7A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000B7584"/>
+        <fgColor rgb="008900E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -151,13 +147,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -528,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -641,31 +637,43 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>首页｜活动｜机会｜我的（回顾/展览并入活动与机会）</t>
+          <t>首页｜课程｜活动｜我的（对齐教育中心：公开课/活动报名/新闻/关于）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>收费入口</t>
+          <t>教育中心模式映射</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>活动票、研修/工作坊、平台会员、支持平台、增值对接包</t>
+          <t>公开课程→课程Tab；定制课程→定制培训页；在线教育→在线学习筛选；活动报名→活动Tab；EE新闻→平台新闻；关于我们→愿景使命价值观</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>收费入口</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>活动票、公开课学费/定金、平台会员、支持平台、增值对接包</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>版本</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>V2.0 · 2026-08 · 去外部机构表述 · 平台化改版</t>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>V2.2 · 2026-08 · NYU Violet 强化 · 教育中心板块模式</t>
         </is>
       </c>
     </row>
@@ -4872,6 +4880,270 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>住房政策研究中心 · 公开新闻精选（可放入小程序动态）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>据公开报道整理；小程序内点击可复制检索词，引导用户自行查阅原文。不代替官方口径。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>摘要</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>公开检索提示</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>来源说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2009.08.29</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>揭牌成立</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>复旦大学住房政策研究中心正式揭牌</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>光华楼揭牌；刘志峰与秦绍德共同揭牌；原则为学术性、中立性、公益性；方向含住房保障、公共住房、市场调控、住房金融等。</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>复旦大学住房政策研究中心 揭牌</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>复旦大学社会科学高等研究院等公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2009.12</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>专题论坛</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>第二期住房政策专题论坛：上海住房政策未来展望与改进分析</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>学界、政策部门与行业专家共议政策框架；围绕上海“十二五”住房政策建议稿征求意见。</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>复旦大学住房政策研究中心 第二期论坛</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>中心公开活动报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2010–2011</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>研究成果</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>发布「复旦-同策上海均质住房价格指数」试行成果</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>基于上海新建市场化商品住宅全样本测算均质价格指数，讨论公共信息服务价值。</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>复旦-同策 上海均质住房价格指数</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>公开发布会报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2011.08</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>国际研讨</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>首届「公共住房的未来」国际研讨会（香港）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>与香港城市大学联合发起；十余个国家与地区专家出席；议题含上海公屋/公积金与国际比较。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>公共住房的未来 国际研讨会 复旦</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>公开会议报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2011–2012</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>国际交流</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>印度住房部代表团来访交流公共住房经验</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>就中国公共住房框架、上海公租房、融资与管理互鉴交流。</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>复旦大学住房政策研究中心 印度代表团</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>公开交流报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2011.08</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>政策研讨</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>「公共住房的未来」研讨：保障房建设动机与国际教训</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>讨论公共住房民生/预防/发展三重作用，强调可持续运营与避免低收入聚居。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>复旦大学 公共住房的未来 保障房</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>公开研讨报道</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6458,7 +6730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6521,7 +6793,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>品牌、入口、即将开始、动态</t>
+          <t>找到课程、推荐课程、活动报名、平台新闻</t>
         </is>
       </c>
     </row>
@@ -6533,17 +6805,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>pages/events/events</t>
+          <t>pages/courses/courses</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>课程</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>列表/筛选；含回顾入口</t>
+          <t>公开课程 / 在线学习（教育中心公开课模式）</t>
         </is>
       </c>
     </row>
@@ -6555,17 +6827,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>pages/opportunity/opportunity</t>
+          <t>pages/events/events</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>机会</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>AI/具身/ChinaJoy/领事名录入口</t>
+          <t>活动列表与报名</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6859,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>会员、支持、订单、关于</t>
+          <t>会员、订单、定制入口、关于</t>
         </is>
       </c>
     </row>
@@ -6599,17 +6871,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>pages/event-detail/event-detail</t>
+          <t>pages/course-detail/course-detail</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>活动详情</t>
+          <t>课程详情</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>议程、票种、报名</t>
+          <t>开班/学制/模块/定金与全款</t>
         </is>
       </c>
     </row>
@@ -6621,17 +6893,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>pages/pay/pay</t>
+          <t>pages/customize/customize</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>确认支付</t>
+          <t>定制培训</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>演示支付</t>
+          <t>七步流程 + 意向表</t>
         </is>
       </c>
     </row>
@@ -6643,17 +6915,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>pages/exhibit/exhibit</t>
+          <t>pages/event-detail/event-detail</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>主题展览</t>
+          <t>活动详情</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>线上策展</t>
+          <t>议程、票种、报名</t>
         </is>
       </c>
     </row>
@@ -6665,17 +6937,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>pages/consulates/consulates</t>
+          <t>pages/pay/pay</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>驻沪领事馆</t>
+          <t>确认支付</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>名录：国家+负责人姓名</t>
+          <t>演示支付</t>
         </is>
       </c>
     </row>
@@ -6687,17 +6959,83 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
+          <t>pages/news/news</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>平台新闻</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>中心公开新闻精选</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>子页</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>pages/consulates/consulates</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>驻沪领事馆</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>姓名检索</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>子页</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>pages/opportunity/opportunity</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>产业机会</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>AI/具身/ChinaJoy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>子页</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>pages/about/about</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>关于平台</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>发起主体与原则</t>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>关于我们</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>愿景使命价值观</t>
         </is>
       </c>
     </row>

--- a/output/复旦链接开放协作平台-小程序功能蓝图.xlsx
+++ b/output/复旦链接开放协作平台-小程序功能蓝图.xlsx
@@ -19,6 +19,7 @@
     <sheet name="09 驻沪领事馆名录" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="10 命名与表述规范" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="11 中心公开新闻精选" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12 互动吧特色优点" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -71,7 +72,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +104,11 @@
         <fgColor rgb="008900E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C5A572"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -130,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -151,6 +157,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -524,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -613,7 +622,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>活动发布与回顾 · 主题展示 · 收费报名 · 产业机会墙 · 驻沪领事检索名录</t>
+          <t>活动全链路（学互动吧）· 公开课程/定制（学教育中心）· 产业机会 · 国际对接</t>
         </is>
       </c>
     </row>
@@ -637,7 +646,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>首页｜课程｜活动｜我的（对齐教育中心：公开课/活动报名/新闻/关于）</t>
+          <t>首页｜课程｜活动｜我的</t>
         </is>
       </c>
     </row>
@@ -649,31 +658,43 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>公开课程→课程Tab；定制课程→定制培训页；在线教育→在线学习筛选；活动报名→活动Tab；EE新闻→平台新闻；关于我们→愿景使命价值观</t>
+          <t>公开课程→课程Tab；定制课程→定制培训页；在线教育→在线学习；活动报名→活动Tab；新闻→平台新闻；关于我们→愿景使命</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>收费入口</t>
+          <t>互动吧能力吸收</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>活动票、公开课学费/定金、平台会员、支持平台、增值对接包</t>
+          <t>轻松办活动：模板发布、海报邀请函、多票种售票、核销签到、裂变传播、到场提醒、现场互动、渠道统计、私域沉淀</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>收费入口</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>活动票、公开课学费/定金、平台会员、支持平台、增值对接包</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>版本</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>V2.2 · 2026-08 · NYU Violet 强化 · 教育中心板块模式</t>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>V2.3 · 2026-08 · 补充互动吧特色优点</t>
         </is>
       </c>
     </row>
@@ -722,52 +743,52 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>国家/地区</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>机构类型</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>开馆日期</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>领区范围</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>所在区域（概位）</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>现任负责人（中文）</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>英文名/检索名</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>公开检索提示</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -4674,7 +4695,7 @@
       </c>
     </row>
     <row r="82" ht="48" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>使用说明：小程序内点击「负责人姓名」可复制检索关键词，引导用户去搜索引擎/馆方官网查找；平台不代为建立直接通讯。领团团长：斐济驻沪总领事 陈玉茹。</t>
         </is>
@@ -4912,32 +4933,32 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>摘要</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>公开检索提示</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>来源说明</t>
         </is>
@@ -5132,6 +5153,398 @@
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>公开研讨报道</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>互动吧特色优点 → 复旦链接活动能力吸收表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>学习互动吧「轻松办活动 + 连接人与活动」的全链路能力；品牌仍用复旦链接，不对外挂互动吧名义。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>互动吧特色优点</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>要点说明</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>复旦链接落地方式</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>对主办方价值</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>对参与者价值</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>轻松办活动（零门槛）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>模板化编辑、标准流程，0 经验也能发出专业活动页</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>活动后台模板：论坛/沙龙/产业日/出海/课程发布会</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>降运营门槛、提发布效率</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>活动信息更完整清晰</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>海报/邀请函智能生成</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>二维码、海报、邀请函一键生成，利于朋友圈传播</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>活动详情「生成海报/邀请函」；分享卡片带 NYU Violet 主视觉</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>引爆社交传播</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>转发更方便、更有仪式感</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>立体展示与裂变传播</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>社交分享、召集官转发、画像推荐，让活动人气起来</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>一键分享小程序路径；召集官码；后续可接推荐位</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>获客更稳</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>更容易发现感兴趣的活动</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>多维度报名/售票</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>自定义表单 + 多票种 + 主流支付，解决报名收费难题</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>免费/学生/标准/VIP/对接席；微信支付演示；审核制免费票</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>收费路径清晰可结算</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>选票买票一气呵成</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>验票核销签到</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>电子票 + 扫码验票，现场高效入场</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>我的票夹展示电子票；现场核销码（演示）</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>现场秩序与数据准确</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>入场更快、凭证清晰</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>渠道/分销统计</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>看清每条报名来源渠道价值</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>运营后台：来源渠道、转化漏斗（规划）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>投放与召集可复盘</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>智能到场提醒</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>短信/公众号/行程多渠道提醒，提高到场率</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>小程序订阅消息 + 活动前推送（规划）</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>降低爽约率</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>不错过开场</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>趣味现场互动</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>签到墙、投票、微信上墙、抽奖等活跃现场</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>现场互动模块（P2）；先做签到墙与抽奖演示入口</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>P2 增强</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>现场氛围与传播素材</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>参与感更强</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>粉丝/私域沉淀</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>活动获客→社群/企微→复购转化</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>报名成功引导关注与社群（合规）；会员年费承接复购</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>人脉资产可运营</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>持续获得课程与活动权益</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>交易保障与信用</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>支付监控、退改规则、信用评价提升安心感</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>退改规则公示；订单状态可查；发票申请</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>降低纠纷</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>报名更安心</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5269,17 +5682,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>报名与票种</t>
+          <t>多票种报名售票</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>免费票 / 付费票 / VIP / 审核制</t>
+          <t>免费/付费/VIP/审核制；自定义报名表单</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>活动详情</t>
+          <t>活动详情（学互动吧）</t>
         </is>
       </c>
     </row>
@@ -5291,345 +5704,499 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>活动回顾与相册</t>
+          <t>电子票与核销签到</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>纪要、图集、实录摘要</t>
+          <t>二维码验票、现场签到</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>回顾入口</t>
+          <t>我的票夹 / 签到</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>展示传播</t>
+          <t>活动运营</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>主题展览</t>
+          <t>海报与邀请函</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>线上策展长页（安居、城市、科技均可）</t>
+          <t>一键生成分享海报/邀请函</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>展览页</t>
+          <t>活动详情分享</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>展示传播</t>
+          <t>活动运营</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>动态信息流</t>
+          <t>社交裂变传播</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>活动预告、机会上新、媒体转载</t>
+          <t>微信分享、召集官转发、拼团可选</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>首页动态</t>
+          <t>分享链路</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>产业机会</t>
+          <t>活动运营</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>AI / 大模型机会卡</t>
+          <t>到场提醒</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>算力、模型、应用场景对接入口</t>
+          <t>公众号/短信等多渠道提醒</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>机会 Tab</t>
+          <t>订阅消息</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>产业机会</t>
+          <t>活动运营</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>具身智能机会卡</t>
+          <t>现场互动</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>机器人、外骨骼、实训场景</t>
+          <t>签到墙、抽奖、投票、上墙（规划）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>机会 Tab</t>
+          <t>现场页</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>产业机会</t>
+          <t>活动运营</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>ChinaJoy / 数字娱乐</t>
+          <t>渠道与订单统计</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>展会、招商引资名录、峰会伙伴</t>
+          <t>报名来源追踪、分销统计</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>机会 Tab</t>
+          <t>运营后台</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>产业机会</t>
+          <t>活动运营</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>企业与园区通道</t>
+          <t>活动回顾与相册</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>科技企业、园区、创客岛等合作位</t>
+          <t>纪要、图集、实录摘要</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>机会墙</t>
+          <t>回顾入口</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>国际对接</t>
+          <t>私域运营</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>驻沪领事检索名录</t>
+          <t>参会者沉淀</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>国家 + 负责人姓名，不含直接联系方式</t>
+          <t>报名后引导关注/社群（合规）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>领事馆页</t>
+          <t>我的 / 社群入口</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>国际对接</t>
+          <t>展示传播</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>出海专题活动</t>
+          <t>主题展览</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>国别推介、商务论坛、会客厅</t>
+          <t>线上策展长页</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>活动类型</t>
+          <t>展览页</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>知识服务</t>
+          <t>展示传播</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>公开研修 / 工作坊</t>
+          <t>动态信息流</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>政策、产业、出海主题培训</t>
+          <t>活动预告、机会上新、媒体转载</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>学习入口</t>
+          <t>首页动态</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>知识服务</t>
+          <t>产业机会</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>定制意向表</t>
+          <t>AI / 大模型机会卡</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>政府/企业定制课题与培训线索</t>
+          <t>算力、模型、应用场景对接入口</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>表单</t>
+          <t>机会 Tab</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>会员与收费</t>
+          <t>产业机会</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>平台会员</t>
+          <t>具身智能机会卡</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>优先报名、资料包、部分回放</t>
+          <t>机器人、外骨骼、实训场景</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>机会 Tab</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>会员与收费</t>
+          <t>产业机会</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>支持平台</t>
+          <t>ChinaJoy / 数字娱乐</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>任意金额支持活动与公共展览</t>
+          <t>展会、招商引资名录、峰会伙伴</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>机会 Tab</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>会员与收费</t>
+          <t>产业机会</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>订单与票据</t>
+          <t>企业与园区通道</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>支付记录、发票申请</t>
+          <t>科技企业、园区、创客岛等合作位</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>我的-订单</t>
+          <t>机会墙</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>个人中心</t>
+          <t>国际对接</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>资料与我的报名</t>
+          <t>驻沪领事检索名录</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>登录、票夹、历史活动</t>
+          <t>国家 + 负责人姓名，不含直接联系方式</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>领事馆页</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>国际对接</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>出海专题活动</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>国别推介、商务论坛、会客厅</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>活动类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>知识服务</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>公开研修 / 工作坊</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>政策、产业、出海主题培训</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>学习入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>知识服务</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>定制意向表</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>政府/企业定制课题与培训线索</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>表单</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>会员与收费</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>平台会员</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>优先报名、资料包、部分回放</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>会员与收费</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>支持平台</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>任意金额支持活动与公共展览</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>会员与收费</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>订单与票据</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>支付记录、发票申请</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>我的-订单</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>个人中心</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>资料与我的报名</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>登录、票夹、历史活动</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t>关于与合规</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>发起主体说明</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>中心简介脚注 + 平台原则</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>关于页</t>
         </is>
@@ -5986,7 +6553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6205,17 +6772,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>详情议程与票种报名</t>
+          <t>详情议程与多票种报名</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>互动吧售票</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>含微信支付演示</t>
+          <t>自定义表单+支付演示</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -6242,27 +6809,27 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>活动回顾与相册</t>
+          <t>电子票/签到核销</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>互动吧验票</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>往期沉淀</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>二维码核销</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -6279,17 +6846,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>主题展览入口</t>
+          <t>海报邀请函与分享裂变</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>互动吧传播</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>线上策展</t>
+          <t>一键生成+微信分享</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -6311,143 +6878,143 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>机会</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>AI / 具身智能机会墙</t>
+          <t>到场提醒（多渠道）</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>产业生态</t>
+          <t>互动吧提醒</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>企业与场景卡片</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>订阅消息/短信规划</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>机会</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ChinaJoy / 展会机会</t>
+          <t>现场互动（签到墙/抽奖）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>展会生态</t>
+          <t>互动吧现场</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>展会与招商卡片</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>气氛与到场体验</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>P2 增强</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>机会</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>驻沪领事检索名录</t>
+          <t>渠道来源统计</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>国际对接</t>
+          <t>互动吧分销统计</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>姓名可检索，无电话邮箱</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>看清每条渠道价值</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
           <t>否</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>机会</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>出海与国别专题</t>
+          <t>活动回顾与相册</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>国际对接</t>
+          <t>平台自身</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>链到相关活动</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>P1 重要</t>
+          <t>往期沉淀</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -6459,59 +7026,59 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>私域</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>公开研修/工作坊列表</t>
+          <t>参会粉丝沉淀</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>知识服务</t>
+          <t>互动吧私域</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>学费/定金</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>报名后社群/关注引导</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>定制意向表</t>
+          <t>主题展览入口</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>知识服务</t>
+          <t>平台自身</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>线索非大额闭环</t>
+          <t>线上策展</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -6521,7 +7088,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>是（线索）</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -6533,22 +7100,22 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>收费</t>
+          <t>机会</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>票种订单中心</t>
+          <t>AI / 具身智能机会墙</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>产业生态</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>订单状态、发票</t>
+          <t>企业与场景卡片</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -6558,7 +7125,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -6570,32 +7137,32 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>收费</t>
+          <t>机会</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>平台会员 / 支持平台</t>
+          <t>ChinaJoy / 展会机会</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>展会生态</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>年费与任意金额</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>P1 重要</t>
+          <t>展会与招商卡片</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -6607,22 +7174,22 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>机会</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>登录资料、我的票、订单</t>
+          <t>驻沪领事检索名录</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>国际对接</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>闭环服务</t>
+          <t>姓名可检索，无电话邮箱</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -6644,32 +7211,32 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>关于</t>
+          <t>机会</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>发起主体与平台原则</t>
+          <t>出海与国别专题</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>可追溯</t>
+          <t>国际对接</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>中心脚注，不抢主品牌</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>链到相关活动</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -6681,35 +7248,257 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>公开研修/工作坊列表</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>知识服务</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>学费/定金</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>定制意向表</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>知识服务</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>线索非大额闭环</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>是（线索）</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>收费</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>票种订单中心</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>平台自身</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>订单状态、发票</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>收费</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>平台会员 / 支持平台</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>平台自身</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>年费与任意金额</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>登录资料、我的票、订单</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>平台自身</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>闭环服务</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>关于</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>发起主体与平台原则</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>可追溯</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>中心脚注，不抢主品牌</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>运营</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>后台活动/机会上架</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>平台运营</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>CMS</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>P0 必做</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -6730,7 +7519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6749,7 +7538,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tab：首页｜活动｜机会｜我的</t>
+          <t>Tab：首页｜课程｜活动｜我的；含活动能力页（互动吧优点吸收）</t>
         </is>
       </c>
     </row>
@@ -6793,7 +7582,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>找到课程、推荐课程、活动报名、平台新闻</t>
+          <t>找到课程、活动能力亮点、推荐课程、活动报名、平台新闻</t>
         </is>
       </c>
     </row>
@@ -6859,7 +7648,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>会员、订单、定制入口、关于</t>
+          <t>会员、票夹/订单、定制入口、活动能力、关于</t>
         </is>
       </c>
     </row>
@@ -6925,7 +7714,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>议程、票种、报名</t>
+          <t>议程、多票种、海报/分享、电子票、报名</t>
         </is>
       </c>
     </row>
@@ -6937,17 +7726,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>pages/pay/pay</t>
+          <t>pages/features/features</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>确认支付</t>
+          <t>活动能力</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>演示支付</t>
+          <t>吸收互动吧特色：轻松办活动→私域沉淀全链路（品牌仍用复旦链接）</t>
         </is>
       </c>
     </row>
@@ -6959,17 +7748,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>pages/news/news</t>
+          <t>pages/pay/pay</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>平台新闻</t>
+          <t>确认支付</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>中心公开新闻精选</t>
+          <t>演示支付</t>
         </is>
       </c>
     </row>
@@ -6981,17 +7770,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>pages/consulates/consulates</t>
+          <t>pages/news/news</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>驻沪领事馆</t>
+          <t>平台新闻</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>姓名检索</t>
+          <t>中心公开新闻精选</t>
         </is>
       </c>
     </row>
@@ -7003,17 +7792,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>pages/opportunity/opportunity</t>
+          <t>pages/consulates/consulates</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>产业机会</t>
+          <t>驻沪领事馆</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>AI/具身/ChinaJoy</t>
+          <t>姓名检索</t>
         </is>
       </c>
     </row>
@@ -7025,15 +7814,37 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
+          <t>pages/opportunity/opportunity</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>产业机会</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>AI/具身/ChinaJoy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>子页</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>pages/about/about</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>关于我们</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>愿景使命价值观</t>
         </is>

--- a/output/复旦链接开放协作平台-小程序功能蓝图.xlsx
+++ b/output/复旦链接开放协作平台-小程序功能蓝图.xlsx
@@ -15,7 +15,7 @@
     <sheet name="05 收费入口设计" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="06 分期与MVP" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="07 内容运营节奏" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08 平台映射总表" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="08 三源对标映射" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="09 驻沪领事馆名录" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="10 命名与表述规范" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="11 中心公开新闻精选" sheetId="12" state="visible" r:id="rId12"/>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -598,103 +598,115 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>先搭平台，再承载活动、产业机会与国际对接——可追溯至中心，但不被「住房政策」字面束缚</t>
+          <t>主骨架学复旦校园服务 + 管院校友中心，活动能力叠加互动吧</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>命名原则</t>
+          <t>对标① 复旦大学小程序</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>专项活动/栏目用平台语言（如「开放协作专项」「产业机会」「国际对接」），避免一切内容都挂「住房政策研究中心」名义</t>
+          <t>服务宫格、常用办事/查询入口、个人中心闭环 → 首页八宫格 + 服务 Tab + 我的</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>核心能力</t>
+          <t>对标② 管院校友中心</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>活动全链路（学互动吧）· 公开课程/定制（学教育中心）· 产业机会 · 国际对接</t>
+          <t>组织 / 活动 / 终身学习 / 职业发展 / 风采 / 支持 / 关于 / 我的</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>用户画像</t>
+          <t>对标③ 互动吧</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>学者与政策研究者、产业与科技企业、出海与招商团队、活动参与者、合作机构</t>
+          <t>轻松办活动、海报邀请函、多票种售票、验票签到、裂变、到场提醒、现场互动、私域沉淀</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Tab 结构</t>
+          <t>命名原则</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>首页｜课程｜活动｜我的</t>
+          <t>对外品牌用复旦链接；栏目可用「协作组织/终身学习/平台风采」等平台语言</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>教育中心模式映射</t>
+          <t>核心能力</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>公开课程→课程Tab；定制课程→定制培训页；在线教育→在线学习；活动报名→活动Tab；新闻→平台新闻；关于我们→愿景使命</t>
+          <t>服务入口 · 协作组织 · 活动全链路 · 终身学习 · 产业机会 · 国际对接</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>互动吧能力吸收</t>
+          <t>用户画像</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>轻松办活动：模板发布、海报邀请函、多票种售票、核销签到、裂变传播、到场提醒、现场互动、渠道统计、私域沉淀</t>
+          <t>研究者、管理者、产业伙伴、出海团队、活动参与者、合作机构</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>收费入口</t>
+          <t>Tab 结构</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>活动票、公开课学费/定金、平台会员、支持平台、增值对接包</t>
+          <t>首页｜服务｜活动｜我的</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>收费入口</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>活动票、公开课学费/定金、平台会员、支持平台、增值对接包</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>版本</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>V2.3 · 2026-08 · 补充互动吧特色优点</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>V2.4 · 2026-08 · 复旦/校友中心主骨架 + 互动吧活动叠加</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4781,7 +4793,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>开放协作专项 · XX 论坛</t>
+          <t>论坛沙龙 / 开放协作专项</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -4793,102 +4805,119 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>中心之友会员</t>
+          <t>校友组织（原机构名）</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>复旦链接会员 / 平台会员</t>
+          <t>协作组织（联络处/社群/同学会）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>会员产品</t>
+          <t>结构对标，品牌自有</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>支持中心</t>
+          <t>校友风采</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>支持平台</t>
+          <t>平台风采</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>捐赠/支持入口</t>
+          <t>结构对标</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>对标管院校友平台…</t>
+          <t>支持学院</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>（删除）按平台能力自述</t>
+          <t>支持平台</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>禁止外部机构对标文案</t>
+          <t>捐赠/支持入口</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>管理学院 / EE 公开课</t>
+          <t>中心之友会员</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>平台公开研修 / 产业工作坊</t>
+          <t>复旦链接会员 / 平台会员</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>培训产品</t>
+          <t>会员产品</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>挂靠管理学院建设…（主文案）</t>
+          <t>对标管院校友平台（禁止照搬品牌）</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>发起主体脚注：住房政策研究中心</t>
+          <t>允许写「结构对标管院校友中心栏目」</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>主文案讲平台，脚注可追溯</t>
+          <t>结构可对标，品牌不挪用</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>住房政策公开课（唯一主线）</t>
+          <t>挂靠管理学院建设…（主文案）</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>城市与产业公开研修（含安居议题）</t>
+          <t>发起主体脚注：住房政策研究中心</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>不被单一议题束缚</t>
+          <t>主文案讲平台，脚注可追溯</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>互动吧（对外挂名）</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>活动能力（复旦链接）</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>能力吸收，不挂互动吧名义</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5638,61 +5667,61 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>快捷入口矩阵</t>
+          <t>服务宫格（对标 eHall）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>活动 / 回顾 / 机会 / 报名收费</t>
+          <t>活动/学习/组织/机会/国际/风采/支持/能力</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>首页四宫格</t>
+          <t>首页八宫格</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>活动运营</t>
+          <t>服务大厅</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>未来活动日历</t>
+          <t>校友中心式栏目分组</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>论坛、沙龙、参访、研修、产业日</t>
+          <t>组织、学习、职业机会、风采、活动与支持</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>活动 Tab</t>
+          <t>服务 Tab</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>活动运营</t>
+          <t>协作组织</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>多票种报名售票</t>
+          <t>地方联络处 / 社群 / 同学会</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>免费/付费/VIP/审核制；自定义报名表单</t>
+          <t>申请加入、聚会信息（演示）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>活动详情（学互动吧）</t>
+          <t>协作组织页</t>
         </is>
       </c>
     </row>
@@ -5704,17 +5733,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>电子票与核销签到</t>
+          <t>未来活动日历</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>二维码验票、现场签到</t>
+          <t>论坛沙龙、产业日、出海、联谊聚会</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>我的票夹 / 签到</t>
+          <t>活动 Tab</t>
         </is>
       </c>
     </row>
@@ -5726,17 +5755,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>海报与邀请函</t>
+          <t>多票种报名售票</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>一键生成分享海报/邀请函</t>
+          <t>免费/付费/VIP/审核制；自定义报名表单</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>活动详情分享</t>
+          <t>活动详情（学互动吧）</t>
         </is>
       </c>
     </row>
@@ -5748,17 +5777,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>社交裂变传播</t>
+          <t>电子票与核销签到</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>微信分享、召集官转发、拼团可选</t>
+          <t>二维码验票、现场签到</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>分享链路</t>
+          <t>我的票夹 / 签到</t>
         </is>
       </c>
     </row>
@@ -5770,17 +5799,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>到场提醒</t>
+          <t>海报与邀请函</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>公众号/短信等多渠道提醒</t>
+          <t>一键生成分享海报/邀请函</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>订阅消息</t>
+          <t>活动详情分享</t>
         </is>
       </c>
     </row>
@@ -5792,17 +5821,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>现场互动</t>
+          <t>社交裂变传播</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>签到墙、抽奖、投票、上墙（规划）</t>
+          <t>微信分享、召集官转发、拼团可选</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>现场页</t>
+          <t>分享链路</t>
         </is>
       </c>
     </row>
@@ -5814,17 +5843,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>渠道与订单统计</t>
+          <t>到场提醒</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>报名来源追踪、分销统计</t>
+          <t>公众号/短信等多渠道提醒</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>运营后台</t>
+          <t>订阅消息</t>
         </is>
       </c>
     </row>
@@ -5836,276 +5865,276 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>活动回顾与相册</t>
+          <t>现场互动</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>纪要、图集、实录摘要</t>
+          <t>签到墙、抽奖、投票、上墙（规划）</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>回顾入口</t>
+          <t>现场页</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>私域运营</t>
+          <t>活动运营</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>参会者沉淀</t>
+          <t>渠道与订单统计</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>报名后引导关注/社群（合规）</t>
+          <t>报名来源追踪、分销统计</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>我的 / 社群入口</t>
+          <t>运营后台</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>展示传播</t>
+          <t>活动运营</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>主题展览</t>
+          <t>活动回顾与相册</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>线上策展长页</t>
+          <t>纪要、图集、实录摘要</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>展览页</t>
+          <t>回顾入口</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>展示传播</t>
+          <t>终身学习</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>动态信息流</t>
+          <t>公开课程 / 在线干货</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>活动预告、机会上新、媒体转载</t>
+          <t>开班、学制、报名支付</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>首页动态</t>
+          <t>课程子页</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>产业机会</t>
+          <t>终身学习</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AI / 大模型机会卡</t>
+          <t>定制培训</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>算力、模型、应用场景对接入口</t>
+          <t>七步流程 + 意向表</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>机会 Tab</t>
+          <t>定制页</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>产业机会</t>
+          <t>职业与机会</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>具身智能机会卡</t>
+          <t>产业机会墙</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>机器人、外骨骼、实训场景</t>
+          <t>AI / 具身 / ChinaJoy</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>机会 Tab</t>
+          <t>机会页</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>产业机会</t>
+          <t>职业与机会</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ChinaJoy / 数字娱乐</t>
+          <t>驻沪领事检索名录</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>展会、招商引资名录、峰会伙伴</t>
+          <t>姓名可检索，无电话邮箱</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>机会 Tab</t>
+          <t>领事馆页</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>产业机会</t>
+          <t>风采展示</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>企业与园区通道</t>
+          <t>故事 / 喜讯 / 观点</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>科技企业、园区、创客岛等合作位</t>
+          <t>对标校友风采</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>机会墙</t>
+          <t>风采页</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>国际对接</t>
+          <t>风采展示</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>驻沪领事检索名录</t>
+          <t>主题展览</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>国家 + 负责人姓名，不含直接联系方式</t>
+          <t>线上策展长页</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>领事馆页</t>
+          <t>展览页</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>国际对接</t>
+          <t>私域运营</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>出海专题活动</t>
+          <t>参会者沉淀</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>国别推介、商务论坛、会客厅</t>
+          <t>报名后引导关注/社群（合规）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>活动类型</t>
+          <t>我的 / 社群入口</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>知识服务</t>
+          <t>会员与收费</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>公开研修 / 工作坊</t>
+          <t>平台会员 / 支持平台</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>政策、产业、出海主题培训</t>
+          <t>年费与任意金额</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>学习入口</t>
+          <t>我的</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>知识服务</t>
+          <t>会员与收费</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>定制意向表</t>
+          <t>订单与票据</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>政府/企业定制课题与培训线索</t>
+          <t>支付记录、发票申请</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>表单</t>
+          <t>我的-订单</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>会员与收费</t>
+          <t>个人中心</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>平台会员</t>
+          <t>更新资料 / 我的组织 / 票夹</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>优先报名、资料包、部分回放</t>
+          <t>对标校友中心我的</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -6117,86 +6146,20 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>会员与收费</t>
+          <t>关于与合规</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>支持平台</t>
+          <t>发起主体说明</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>任意金额支持活动与公共展览</t>
+          <t>中心简介脚注 + 平台原则</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>我的</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>会员与收费</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>订单与票据</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>支付记录、发票申请</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>我的-订单</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>个人中心</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>资料与我的报名</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>登录、票夹、历史活动</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>我的</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>关于与合规</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>发起主体说明</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>中心简介脚注 + 平台原则</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>关于页</t>
         </is>
@@ -6553,7 +6516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6661,17 +6624,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>快捷入口：活动/回顾/机会/收费</t>
+          <t>服务宫格（对标 eHall）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>复旦大学小程序</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>四宫格</t>
+          <t>八宫格直达常用服务</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -6698,17 +6661,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>即将开始 + 动态流</t>
+          <t>资讯速递 + 近期活动 + 终身学习</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>校友中心首页</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>活动与机会混排</t>
+          <t>新闻/活动/课程混排</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -6730,22 +6693,22 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>服务</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>活动列表与筛选</t>
+          <t>服务大厅栏目分组</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>管院校友中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>论坛/沙龙/研修/参访/出海/产业日</t>
+          <t>组织/学习/机会/风采/支持</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -6755,7 +6718,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -6767,32 +6730,32 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>组织</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>详情议程与多票种报名</t>
+          <t>联络处/社群/同学会</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>互动吧售票</t>
+          <t>管院校友中心</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>自定义表单+支付演示</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>申请加入演示</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -6809,22 +6772,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>电子票/签到核销</t>
+          <t>活动列表与筛选</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>互动吧验票</t>
+          <t>校友活动+互动吧</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>二维码核销</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>P1 重要</t>
+          <t>论坛沙龙/产业日/出海/联谊</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -6846,27 +6809,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>海报邀请函与分享裂变</t>
+          <t>详情议程与多票种报名</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>互动吧传播</t>
+          <t>互动吧售票</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>一键生成+微信分享</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>P1 重要</t>
+          <t>自定义表单+支付演示</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -6883,17 +6846,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>到场提醒（多渠道）</t>
+          <t>电子票/签到核销</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>互动吧提醒</t>
+          <t>互动吧验票</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>订阅消息/短信规划</t>
+          <t>二维码核销</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -6903,12 +6866,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6920,22 +6883,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>现场互动（签到墙/抽奖）</t>
+          <t>海报邀请函与分享裂变</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>互动吧现场</t>
+          <t>互动吧传播</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>气氛与到场体验</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>P2 增强</t>
+          <t>一键生成+微信分享</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -6945,7 +6908,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6957,17 +6920,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>渠道来源统计</t>
+          <t>到场提醒（多渠道）</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>互动吧分销统计</t>
+          <t>互动吧提醒</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>看清每条渠道价值</t>
+          <t>订阅消息/短信规划</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -6977,7 +6940,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -6994,22 +6957,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>活动回顾与相册</t>
+          <t>现场互动（签到墙/抽奖）</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>互动吧现场</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>往期沉淀</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>气氛与到场体验</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>P2 增强</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -7019,29 +6982,29 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>私域</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>参会粉丝沉淀</t>
+          <t>渠道来源统计</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>互动吧私域</t>
+          <t>互动吧分销统计</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>报名后社群/关注引导</t>
+          <t>看清每条渠道价值</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -7051,7 +7014,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -7068,7 +7031,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>主题展览入口</t>
+          <t>活动回顾与相册</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -7078,12 +7041,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>线上策展</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>P1 重要</t>
+          <t>往期沉淀</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -7100,22 +7063,22 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>机会</t>
+          <t>学习</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>AI / 具身智能机会墙</t>
+          <t>公开课程 / 在线干货</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>产业生态</t>
+          <t>校友终身学习</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>企业与场景卡片</t>
+          <t>学费/定金</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -7125,7 +7088,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -7137,32 +7100,32 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>机会</t>
+          <t>学习</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ChinaJoy / 展会机会</t>
+          <t>定制培训意向</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>展会生态</t>
+          <t>校友/教育中心</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>展会与招商卡片</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>七步流程线索</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>是（线索）</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -7179,17 +7142,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>驻沪领事检索名录</t>
+          <t>产业机会墙</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>国际对接</t>
+          <t>职业发展延伸</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>姓名可检索，无电话邮箱</t>
+          <t>AI/具身/ChinaJoy</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -7199,7 +7162,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -7216,7 +7179,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>出海与国别专题</t>
+          <t>驻沪领事检索名录</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -7226,17 +7189,17 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>链到相关活动</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>P1 重要</t>
+          <t>姓名可检索，无电话邮箱</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -7248,32 +7211,32 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>风采</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>公开研修/工作坊列表</t>
+          <t>故事/喜讯/观点</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>知识服务</t>
+          <t>校友风采</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>学费/定金</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>内容运营</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -7285,22 +7248,22 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>风采</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>定制意向表</t>
+          <t>主题展览</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>知识服务</t>
+          <t>平台自身</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>线索非大额闭环</t>
+          <t>线上策展</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -7310,7 +7273,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>是（线索）</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -7322,37 +7285,37 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>收费</t>
+          <t>私域</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>票种订单中心</t>
+          <t>参会粉丝沉淀</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>互动吧私域</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>订单状态、发票</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>报名后社群/关注引导</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7327,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>平台会员 / 支持平台</t>
+          <t>票种订单中心</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -7374,12 +7337,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>年费与任意金额</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>P1 重要</t>
+          <t>订单状态、发票</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -7396,32 +7359,32 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>收费</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>登录资料、我的票、订单</t>
+          <t>平台会员 / 支持平台</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>平台自身</t>
+          <t>支持学院对标</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>闭环服务</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>P0 必做</t>
+          <t>年费与任意金额</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>P1 重要</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -7433,22 +7396,22 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>关于</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>发起主体与平台原则</t>
+          <t>更新资料/组织/票夹/订单</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>可追溯</t>
+          <t>校友中心我的</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>中心脚注，不抢主品牌</t>
+          <t>闭环服务</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -7470,35 +7433,72 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>关于</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>发起主体与平台原则</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>可追溯</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>中心脚注，不抢主品牌</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>P0 必做</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>运营</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>后台活动/机会上架</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>平台运营</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>CMS</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>P0 必做</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -7519,7 +7519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7538,7 +7538,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tab：首页｜课程｜活动｜我的；含活动能力页（互动吧优点吸收）</t>
+          <t>Tab：首页｜服务｜活动｜我的（复旦/校友骨架 + 互动吧活动）</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>找到课程、活动能力亮点、推荐课程、活动报名、平台新闻</t>
+          <t>eHall 式服务宫格 + 资讯 + 近期活动 + 终身学习</t>
         </is>
       </c>
     </row>
@@ -7594,17 +7594,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>pages/courses/courses</t>
+          <t>pages/services/services</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>课程</t>
+          <t>服务</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>公开课程 / 在线学习（教育中心公开课模式）</t>
+          <t>校友中心式栏目大厅</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>活动列表与报名</t>
+          <t>活动列表 + 互动吧能力提示</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>会员、票夹/订单、定制入口、活动能力、关于</t>
+          <t>资料、组织、票夹、会员、支持</t>
         </is>
       </c>
     </row>
@@ -7660,17 +7660,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>pages/course-detail/course-detail</t>
+          <t>pages/courses/courses</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>课程详情</t>
+          <t>终身学习</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>开班/学制/模块/定金与全款</t>
+          <t>公开课程 / 在线学习</t>
         </is>
       </c>
     </row>
@@ -7682,17 +7682,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>pages/customize/customize</t>
+          <t>pages/course-detail/course-detail</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>定制培训</t>
+          <t>课程详情</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>七步流程 + 意向表</t>
+          <t>开班/学制/模块/定金与全款</t>
         </is>
       </c>
     </row>
@@ -7704,17 +7704,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>pages/event-detail/event-detail</t>
+          <t>pages/customize/customize</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>活动详情</t>
+          <t>定制培训</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>议程、多票种、海报/分享、电子票、报名</t>
+          <t>七步流程 + 意向表</t>
         </is>
       </c>
     </row>
@@ -7726,17 +7726,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>pages/features/features</t>
+          <t>pages/event-detail/event-detail</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>活动能力</t>
+          <t>活动详情</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>吸收互动吧特色：轻松办活动→私域沉淀全链路（品牌仍用复旦链接）</t>
+          <t>议程、多票种、海报/分享、电子票</t>
         </is>
       </c>
     </row>
@@ -7748,17 +7748,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>pages/pay/pay</t>
+          <t>pages/features/features</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>确认支付</t>
+          <t>活动能力</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>演示支付</t>
+          <t>互动吧优点吸收说明</t>
         </is>
       </c>
     </row>
@@ -7770,17 +7770,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>pages/news/news</t>
+          <t>pages/orgs/orgs</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>平台新闻</t>
+          <t>协作组织</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>中心公开新闻精选</t>
+          <t>联络处/社群/同学会</t>
         </is>
       </c>
     </row>
@@ -7792,17 +7792,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>pages/consulates/consulates</t>
+          <t>pages/stories/stories</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>驻沪领事馆</t>
+          <t>平台风采</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>姓名检索</t>
+          <t>故事/喜讯/观点</t>
         </is>
       </c>
     </row>
@@ -7814,17 +7814,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>pages/opportunity/opportunity</t>
+          <t>pages/pay/pay</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>产业机会</t>
+          <t>确认支付</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AI/具身/ChinaJoy</t>
+          <t>演示支付</t>
         </is>
       </c>
     </row>
@@ -7836,17 +7836,127 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>pages/news/news</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>平台新闻</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>中心公开新闻精选</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>子页</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>pages/consulates/consulates</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>驻沪领事馆</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>姓名检索</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>子页</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>pages/opportunity/opportunity</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>产业机会</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>AI/具身/ChinaJoy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>子页</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>pages/about/about</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>关于我们</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>愿景使命价值观</t>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>愿景使命与对标说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>子页</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>pages/exhibit/exhibit</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>主题展览</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>线上策展</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>子页</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>pages/archive/archive</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>活动回顾</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>往期纪要</t>
         </is>
       </c>
     </row>
@@ -8214,7 +8324,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>首页/活动/机会/我的 + 支付演示 + 领事名录</t>
+          <t>首页/服务/活动/我的 + 互动吧能力演示 + 领事名录</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -8224,7 +8334,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>本仓库</t>
+          <t>本仓库 V2.4</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8346,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>真实登录支付、后台上架、消息订阅</t>
+          <t>真实登录支付、后台上架、消息订阅、组织审核</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -8258,12 +8368,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>产业机会墙深化、出海专题、会员</t>
+          <t>产业机会墙深化、出海专题、会员与风采运营</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>活动+机会双轮</t>
+          <t>服务+活动双轮</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -8479,46 +8589,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>平台模块 → 内容与价值</t>
+          <t>三源对标映射：复旦大学小程序 × 管院校友中心 × 互动吧 → 复旦链接</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>统一追溯到「复旦链接」平台专项</t>
+          <t>结构与能力参考；对外品牌统一为复旦链接，不挪用原小程序品牌名义</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>平台模块</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>承载内容</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>小程序功能</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>对标来源</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>原栏目/能力</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>复旦链接落地</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>价值说明</t>
         </is>
@@ -8527,176 +8637,286 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>复旦大学小程序(eHall)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>论坛/沙龙/研修/出海/产业日</t>
+          <t>服务宫格 / 办事入口</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>列表、详情、票种、回顾</t>
+          <t>首页八宫格 + 服务 Tab</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>平台主轴</t>
+          <t>降低找功能成本</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>机会·AI</t>
+          <t>复旦大学小程序</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>大模型、智算、应用</t>
+          <t>个人中心闭环</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>机会卡片、跳转活动</t>
+          <t>我的：资料/票夹/订单</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>链接科技企业与场景</t>
+          <t>服务闭环</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>机会·具身</t>
+          <t>管院校友中心</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>机器人、外骨骼、实训</t>
+          <t>校友组织</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>机会卡片、体验展入口</t>
+          <t>协作组织（联络处/社群/同学会）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>链接具身智能生态</t>
+          <t>人脉与归属</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>机会·ChinaJoy</t>
+          <t>管院校友中心</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>展会、招商名录、峰会伙伴</t>
+          <t>校友活动</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>展会专区、对接包</t>
+          <t>活动 Tab（论坛/产业日/出海/联谊）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>链接数字娱乐与投资</t>
+          <t>主运营触点</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>机会·国际</t>
+          <t>管院校友中心</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>驻沪领事、出海国别</t>
+          <t>终身学习</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>领事名录（姓名检索）</t>
+          <t>公开课 / 在线 / 定制</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>链接开放与出海</t>
+          <t>持续学习</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>展示</t>
+          <t>管院校友中心</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>主题展、成果精选</t>
+          <t>职业发展</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>展览页、动态</t>
+          <t>产业机会墙 + 对接席</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>传播与沉淀</t>
+          <t>职业与产业链接</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>收费</t>
+          <t>管院校友中心</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>票务/会员/支持/对接包</t>
+          <t>校友风采</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>支付与订单</t>
+          <t>平台风采（故事/喜讯/观点）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>可持续运营</t>
+          <t>内容传播</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>可追溯</t>
+          <t>管院校友中心</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>发起主体脚注</t>
+          <t>支持学院 / 关于我们</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>关于页</t>
+          <t>支持平台 + 关于页</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>一切专项可追溯至平台与中心</t>
+          <t>可持续与可追溯</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>互动吧</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>轻松办活动/海报/裂变</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>活动模板 + 海报分享</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>获客与传播</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>互动吧</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>多票种售票/验票签到</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>票种选择 + 电子票核销</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>收费与到场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>互动吧</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>现场互动/私域沉淀</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>签到墙抽奖演示 + 会员复购</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>氛围与复购</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>平台自身</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>住房/城市议题</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>论坛与公开研修垂直之一</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>中心特色</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>平台自身</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>国际对接</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>驻沪领事检索名录</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>出海与开放</t>
         </is>
       </c>
     </row>

--- a/output/复旦链接开放协作平台-小程序功能蓝图.xlsx
+++ b/output/复旦链接开放协作平台-小程序功能蓝图.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>V2.4 · 2026-08 · 复旦/校友中心主骨架 + 互动吧活动叠加</t>
+          <t>V3.0 集合版 · 2026-08 · 综合复旦校园服务/校友中心/教育中心/互动吧</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>本仓库 V2.4</t>
+          <t>本仓库 V3.0 集合版</t>
         </is>
       </c>
     </row>
